--- a/output/reports/cargo_classification_results.xlsx
+++ b/output/reports/cargo_classification_results.xlsx
@@ -7,10 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="分类汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大货物订单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中货物订单" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="小货物订单" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大货物订单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中货物订单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="小货物订单" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,101 +431,321 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>分类</t>
+          <t>pickup_delivery</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>订单数量</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>总体积(m³)</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>体积占比</t>
+          <t>cargo_type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>volume_dm3</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>weight_kg</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>volume_m3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>unit_converted</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>order_id</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>item_type</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>order_total_volume_m3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>order_total_weight_kg</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>density</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>processed_timestamp</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>大货物</t>
+          <t>取货需求</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>104.196005</v>
       </c>
       <c r="C2" t="n">
-        <v>471.9332</v>
+        <v>30.539113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>69.6%</t>
-        </is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="F2" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2793</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.07856</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2793</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ORDER_0036</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>219.41808</v>
+      </c>
+      <c r="N2" t="n">
+        <v>66249.95999999999</v>
+      </c>
+      <c r="O2" t="n">
+        <v>301.9348230405445</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>中货物</t>
+          <t>取货需求</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>104.036469</v>
       </c>
       <c r="C3" t="n">
-        <v>107.59078</v>
+        <v>30.867638</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15.9%</t>
-        </is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="F3" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1994.02</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.07298</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1994</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ORDER_0027</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>145.52212</v>
+      </c>
+      <c r="N3" t="n">
+        <v>37227.98</v>
+      </c>
+      <c r="O3" t="n">
+        <v>255.8235097859207</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>小货物</t>
+          <t>取货需求</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>33</v>
+        <v>104.286461</v>
       </c>
       <c r="C4" t="n">
-        <v>98.658912</v>
+        <v>30.784712</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14.5%</t>
-        </is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="F4" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1425</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.03928</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1425</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>ORDER_0032</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>55.974</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15347.25</v>
+      </c>
+      <c r="O4" t="n">
+        <v>274.1853290686016</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>总计</t>
+          <t>取货需求</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>44</v>
+        <v>104.164075</v>
       </c>
       <c r="C5" t="n">
-        <v>678.1828919999999</v>
+        <v>30.802111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>68.16</v>
+      </c>
+      <c r="F5" t="n">
+        <v>68.16</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1565</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.0326</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1565</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ORDER_0026</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>51.01900000000001</v>
+      </c>
+      <c r="N5" t="n">
+        <v>106670.4</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2090.797481877377</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>45919.97338141783</v>
       </c>
     </row>
   </sheetData>
@@ -540,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -632,55 +851,55 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104.196005</v>
+        <v>104.558069</v>
       </c>
       <c r="C2" t="n">
-        <v>30.539113</v>
+        <v>30.399125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>酒水</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>23.72</v>
+        <v>7.42</v>
       </c>
       <c r="F2" t="n">
-        <v>23.72</v>
+        <v>7.42</v>
       </c>
       <c r="G2" t="n">
-        <v>2793</v>
+        <v>470</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07856</v>
+        <v>0.049</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>2793</v>
+        <v>470</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ORDER_0036</t>
+          <t>ORDER_0040</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>酒水</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="M2" t="n">
-        <v>219.41808</v>
+        <v>23.03</v>
       </c>
       <c r="N2" t="n">
-        <v>66249.95999999999</v>
+        <v>3487.4</v>
       </c>
       <c r="O2" t="n">
-        <v>301.9348230405445</v>
+        <v>151.4285683381925</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="3">
@@ -690,10 +909,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104.036469</v>
+        <v>104.609837</v>
       </c>
       <c r="C3" t="n">
-        <v>30.867638</v>
+        <v>30.737656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -701,26 +920,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18.67</v>
+        <v>5.97</v>
       </c>
       <c r="F3" t="n">
-        <v>18.67</v>
+        <v>5.97</v>
       </c>
       <c r="G3" t="n">
-        <v>1994.02</v>
+        <v>796.03</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07298</v>
+        <v>0.02594</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>1994</v>
+        <v>796</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>ORDER_0027</t>
+          <t>ORDER_0033</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -729,16 +948,16 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>145.52212</v>
+        <v>20.64824</v>
       </c>
       <c r="N3" t="n">
-        <v>37227.98</v>
+        <v>4752.12</v>
       </c>
       <c r="O3" t="n">
-        <v>255.8235097859207</v>
+        <v>230.1464830321325</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="4">
@@ -748,113 +967,287 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>104.286461</v>
+        <v>104.28116</v>
       </c>
       <c r="C4" t="n">
-        <v>30.784712</v>
+        <v>30.851558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>酒水</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>10.77</v>
+        <v>10.35</v>
       </c>
       <c r="F4" t="n">
-        <v>10.77</v>
+        <v>10.35</v>
       </c>
       <c r="G4" t="n">
-        <v>1425</v>
+        <v>420</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03928</v>
+        <v>0.042</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1425</v>
+        <v>420</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ORDER_0032</t>
+          <t>ORDER_0031</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>酒水</t>
+          <t>食品</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>55.974</v>
+        <v>17.64</v>
       </c>
       <c r="N4" t="n">
-        <v>15347.25</v>
+        <v>4347</v>
       </c>
       <c r="O4" t="n">
-        <v>274.1853290686016</v>
+        <v>246.4285655612246</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>配送需求</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>104.0668</v>
+      </c>
+      <c r="C5" t="n">
+        <v>30.76405</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>310</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>310</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ORDER_0011</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>食品</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>13.02</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1922</v>
+      </c>
+      <c r="O5" t="n">
+        <v>147.6190441043085</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>45919.97338141783</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>取货需求</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>104.164075</v>
-      </c>
-      <c r="C5" t="n">
-        <v>30.802111</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="B6" t="n">
+        <v>104.086109</v>
+      </c>
+      <c r="C6" t="n">
+        <v>30.689311</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>食品</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>68.16</v>
-      </c>
-      <c r="F5" t="n">
-        <v>68.16</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1565</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.0326</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1565</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ORDER_0026</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="E6" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="G6" t="n">
+        <v>322</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>322</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ORDER_0022</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>食品</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>51.01900000000001</v>
-      </c>
-      <c r="N5" t="n">
-        <v>106670.4</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2090.797481877377</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>45918.93223118466</v>
+      <c r="M6" t="n">
+        <v>11.592</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1696.94</v>
+      </c>
+      <c r="O6" t="n">
+        <v>146.3888848225309</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>45919.97338141783</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>配送需求</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>104.1591</v>
+      </c>
+      <c r="C7" t="n">
+        <v>30.84101</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>12</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>763</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>763</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ORDER_0012</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>11.445</v>
+      </c>
+      <c r="N7" t="n">
+        <v>9156</v>
+      </c>
+      <c r="O7" t="n">
+        <v>799.9999466666703</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>45919.97338141783</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>取货需求</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>104.269026</v>
+      </c>
+      <c r="C8" t="n">
+        <v>30.893214</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="F8" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="G8" t="n">
+        <v>522</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.01957</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>522</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ORDER_0030</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>酒水</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>10.21554</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2625.66</v>
+      </c>
+      <c r="O8" t="n">
+        <v>257.0260471626956</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>45919.97338141783</v>
       </c>
     </row>
   </sheetData>
@@ -868,508 +1261,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>pickup_delivery</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>longitude</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>latitude</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>cargo_type</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>volume_dm3</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>weight_kg</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>volume_m3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>unit_converted</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>order_id</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>item_type</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>order_total_volume_m3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>order_total_weight_kg</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>density</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>processed_timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>取货需求</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>104.558069</v>
-      </c>
-      <c r="C2" t="n">
-        <v>30.399125</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7.42</v>
-      </c>
-      <c r="G2" t="n">
-        <v>470</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-      <c r="J2" t="n">
-        <v>470</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>ORDER_0040</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>23.03</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3487.4</v>
-      </c>
-      <c r="O2" t="n">
-        <v>151.4285683381925</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>45918.93223118466</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>取货需求</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>104.609837</v>
-      </c>
-      <c r="C3" t="n">
-        <v>30.737656</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>酒水</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="F3" t="n">
-        <v>5.97</v>
-      </c>
-      <c r="G3" t="n">
-        <v>796.03</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.02594</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J3" t="n">
-        <v>796</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ORDER_0033</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>酒水</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
-        <v>20.64824</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4752.12</v>
-      </c>
-      <c r="O3" t="n">
-        <v>230.1464830321325</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>45918.93223118466</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>取货需求</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>104.28116</v>
-      </c>
-      <c r="C4" t="n">
-        <v>30.851558</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="F4" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="G4" t="n">
-        <v>420</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" t="n">
-        <v>420</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>ORDER_0031</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="M4" t="n">
-        <v>17.64</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4347</v>
-      </c>
-      <c r="O4" t="n">
-        <v>246.4285655612246</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>45918.93223118466</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>配送需求</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>104.0668</v>
-      </c>
-      <c r="C5" t="n">
-        <v>30.76405</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="G5" t="n">
-        <v>310</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>310</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>ORDER_0011</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>13.02</v>
-      </c>
-      <c r="N5" t="n">
-        <v>1922</v>
-      </c>
-      <c r="O5" t="n">
-        <v>147.6190441043085</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>45918.93223118466</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>取货需求</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>104.086109</v>
-      </c>
-      <c r="C6" t="n">
-        <v>30.689311</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="G6" t="n">
-        <v>322</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" t="n">
-        <v>322</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ORDER_0022</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>食品</t>
-        </is>
-      </c>
-      <c r="M6" t="n">
-        <v>11.592</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1696.94</v>
-      </c>
-      <c r="O6" t="n">
-        <v>146.3888848225309</v>
-      </c>
-      <c r="P6" s="2" t="n">
-        <v>45918.93223118466</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>配送需求</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>104.1591</v>
-      </c>
-      <c r="C7" t="n">
-        <v>30.84101</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>酒水</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>12</v>
-      </c>
-      <c r="F7" t="n">
-        <v>12</v>
-      </c>
-      <c r="G7" t="n">
-        <v>763</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="I7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>763</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>ORDER_0012</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>酒水</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>11.445</v>
-      </c>
-      <c r="N7" t="n">
-        <v>9156</v>
-      </c>
-      <c r="O7" t="n">
-        <v>799.9999466666703</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>45918.93223118466</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>取货需求</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>104.269026</v>
-      </c>
-      <c r="C8" t="n">
-        <v>30.893214</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>酒水</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="F8" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="G8" t="n">
-        <v>522</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.01957</v>
-      </c>
-      <c r="I8" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>522</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>ORDER_0030</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>酒水</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>10.21554</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2625.66</v>
-      </c>
-      <c r="O8" t="n">
-        <v>257.0260471626956</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>45918.93223118466</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1510,7 +1401,7 @@
         <v>1549.666580574079</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="3">
@@ -1568,7 +1459,7 @@
         <v>558.1395132504065</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="4">
@@ -1626,7 +1517,7 @@
         <v>323.4210356094192</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="5">
@@ -1684,7 +1575,7 @@
         <v>338.6110922993837</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="6">
@@ -1742,7 +1633,7 @@
         <v>186.519454589224</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="7">
@@ -1800,7 +1691,7 @@
         <v>658.3079370971024</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="8">
@@ -1858,7 +1749,7 @@
         <v>364.166636319447</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="9">
@@ -1916,7 +1807,7 @@
         <v>337.9999774666682</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="10">
@@ -1974,7 +1865,7 @@
         <v>359.090876446284</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="11">
@@ -2032,7 +1923,7 @@
         <v>286.1110952160503</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="12">
@@ -2090,7 +1981,7 @@
         <v>372.4999689583359</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="13">
@@ -2148,7 +2039,7 @@
         <v>999.9998039216071</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="14">
@@ -2206,7 +2097,7 @@
         <v>339.1666384027802</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="15">
@@ -2264,7 +2155,7 @@
         <v>260.5768980214521</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="16">
@@ -2322,7 +2213,7 @@
         <v>199.3516856279023</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="17">
@@ -2380,7 +2271,7 @@
         <v>1115.999898545464</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="18">
@@ -2438,7 +2329,7 @@
         <v>280.8333099305575</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="19">
@@ -2496,7 +2387,7 @@
         <v>217.241371819263</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="20">
@@ -2554,7 +2445,7 @@
         <v>1190.475907029546</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="21">
@@ -2612,7 +2503,7 @@
         <v>363.3332929629674</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="22">
@@ -2670,7 +2561,7 @@
         <v>1124.99971875007</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="23">
@@ -2728,7 +2619,7 @@
         <v>256.2091168354095</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="24">
@@ -2786,7 +2677,7 @@
         <v>1333.332929293052</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="25">
@@ -2844,7 +2735,7 @@
         <v>1099.999633333455</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="26">
@@ -2902,7 +2793,7 @@
         <v>381.249952343756</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="27">
@@ -2960,7 +2851,7 @@
         <v>1133.332955555682</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="28">
@@ -3018,7 +2909,7 @@
         <v>349.9999416666764</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="29">
@@ -3076,7 +2967,7 @@
         <v>1499.999250000375</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="30">
@@ -3134,7 +3025,7 @@
         <v>394.7367382271742</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="31">
@@ -3192,7 +3083,7 @@
         <v>1199.999760000048</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="32">
@@ -3250,7 +3141,7 @@
         <v>288.3434698332915</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="33">
@@ -3308,7 +3199,7 @@
         <v>489.9997550001225</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
     <row r="34">
@@ -3366,7 +3257,7 @@
         <v>2249.999718750035</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>45918.93223118466</v>
+        <v>45919.97338141783</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cargo_classification_results.xlsx
+++ b/output/reports/cargo_classification_results.xlsx
@@ -571,7 +571,7 @@
         <v>301.9348230405445</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         <v>255.8235097859207</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         <v>274.1853290686016</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         <v>2090.797481877377</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +899,7 @@
         <v>151.4285683381925</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="3">
@@ -957,7 +957,7 @@
         <v>230.1464830321325</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="4">
@@ -1015,7 +1015,7 @@
         <v>246.4285655612246</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="5">
@@ -1073,7 +1073,7 @@
         <v>147.6190441043085</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="6">
@@ -1131,7 +1131,7 @@
         <v>146.3888848225309</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1189,7 @@
         <v>799.9999466666703</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="8">
@@ -1247,7 +1247,7 @@
         <v>257.0260471626956</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
   </sheetData>
@@ -1401,7 +1401,7 @@
         <v>1549.666580574079</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="3">
@@ -1459,7 +1459,7 @@
         <v>558.1395132504065</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="4">
@@ -1517,7 +1517,7 @@
         <v>323.4210356094192</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="5">
@@ -1575,7 +1575,7 @@
         <v>338.6110922993837</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="6">
@@ -1633,7 +1633,7 @@
         <v>186.519454589224</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="7">
@@ -1691,7 +1691,7 @@
         <v>658.3079370971024</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="8">
@@ -1749,7 +1749,7 @@
         <v>364.166636319447</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="9">
@@ -1807,7 +1807,7 @@
         <v>337.9999774666682</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1865,7 @@
         <v>359.090876446284</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="11">
@@ -1923,7 +1923,7 @@
         <v>286.1110952160503</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="12">
@@ -1981,7 +1981,7 @@
         <v>372.4999689583359</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="13">
@@ -2039,7 +2039,7 @@
         <v>999.9998039216071</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="14">
@@ -2097,7 +2097,7 @@
         <v>339.1666384027802</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="15">
@@ -2155,7 +2155,7 @@
         <v>260.5768980214521</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="16">
@@ -2213,7 +2213,7 @@
         <v>199.3516856279023</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="17">
@@ -2271,7 +2271,7 @@
         <v>1115.999898545464</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="18">
@@ -2329,7 +2329,7 @@
         <v>280.8333099305575</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="19">
@@ -2387,7 +2387,7 @@
         <v>217.241371819263</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="20">
@@ -2445,7 +2445,7 @@
         <v>1190.475907029546</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="21">
@@ -2503,7 +2503,7 @@
         <v>363.3332929629674</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="22">
@@ -2561,7 +2561,7 @@
         <v>1124.99971875007</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="23">
@@ -2619,7 +2619,7 @@
         <v>256.2091168354095</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="24">
@@ -2677,7 +2677,7 @@
         <v>1333.332929293052</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="25">
@@ -2735,7 +2735,7 @@
         <v>1099.999633333455</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="26">
@@ -2793,7 +2793,7 @@
         <v>381.249952343756</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="27">
@@ -2851,7 +2851,7 @@
         <v>1133.332955555682</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="28">
@@ -2909,7 +2909,7 @@
         <v>349.9999416666764</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="29">
@@ -2967,7 +2967,7 @@
         <v>1499.999250000375</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="30">
@@ -3025,7 +3025,7 @@
         <v>394.7367382271742</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="31">
@@ -3083,7 +3083,7 @@
         <v>1199.999760000048</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="32">
@@ -3141,7 +3141,7 @@
         <v>288.3434698332915</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="33">
@@ -3199,7 +3199,7 @@
         <v>489.9997550001225</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
     <row r="34">
@@ -3257,7 +3257,7 @@
         <v>2249.999718750035</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>45919.97338141783</v>
+        <v>45922.72111330232</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cargo_classification_results.xlsx
+++ b/output/reports/cargo_classification_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大货物订单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中货物订单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="小货物订单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="大货物订单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="中货物订单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="小货物订单" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,7 +571,7 @@
         <v>301.9348230405445</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         <v>255.8235097859207</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         <v>274.1853290686016</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         <v>2090.797481877377</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +899,7 @@
         <v>151.4285683381925</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="3">
@@ -957,7 +957,7 @@
         <v>230.1464830321325</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="4">
@@ -1015,7 +1015,7 @@
         <v>246.4285655612246</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="5">
@@ -1073,7 +1073,7 @@
         <v>147.6190441043085</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="6">
@@ -1131,7 +1131,7 @@
         <v>146.3888848225309</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1189,7 @@
         <v>799.9999466666703</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="8">
@@ -1247,7 +1247,7 @@
         <v>257.0260471626956</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
   </sheetData>
@@ -1401,7 +1401,7 @@
         <v>1549.666580574079</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="3">
@@ -1459,7 +1459,7 @@
         <v>558.1395132504065</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="4">
@@ -1517,7 +1517,7 @@
         <v>323.4210356094192</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="5">
@@ -1575,7 +1575,7 @@
         <v>338.6110922993837</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="6">
@@ -1633,7 +1633,7 @@
         <v>186.519454589224</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="7">
@@ -1691,7 +1691,7 @@
         <v>658.3079370971024</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="8">
@@ -1749,7 +1749,7 @@
         <v>364.166636319447</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="9">
@@ -1807,7 +1807,7 @@
         <v>337.9999774666682</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1865,7 @@
         <v>359.090876446284</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="11">
@@ -1923,7 +1923,7 @@
         <v>286.1110952160503</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="12">
@@ -1981,7 +1981,7 @@
         <v>372.4999689583359</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="13">
@@ -2039,7 +2039,7 @@
         <v>999.9998039216071</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="14">
@@ -2097,7 +2097,7 @@
         <v>339.1666384027802</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="15">
@@ -2155,7 +2155,7 @@
         <v>260.5768980214521</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="16">
@@ -2213,7 +2213,7 @@
         <v>199.3516856279023</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="17">
@@ -2271,7 +2271,7 @@
         <v>1115.999898545464</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="18">
@@ -2329,7 +2329,7 @@
         <v>280.8333099305575</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="19">
@@ -2387,7 +2387,7 @@
         <v>217.241371819263</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="20">
@@ -2445,7 +2445,7 @@
         <v>1190.475907029546</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="21">
@@ -2503,7 +2503,7 @@
         <v>363.3332929629674</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="22">
@@ -2561,7 +2561,7 @@
         <v>1124.99971875007</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="23">
@@ -2619,7 +2619,7 @@
         <v>256.2091168354095</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="24">
@@ -2677,7 +2677,7 @@
         <v>1333.332929293052</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="25">
@@ -2735,7 +2735,7 @@
         <v>1099.999633333455</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="26">
@@ -2793,7 +2793,7 @@
         <v>381.249952343756</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="27">
@@ -2851,7 +2851,7 @@
         <v>1133.332955555682</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="28">
@@ -2909,7 +2909,7 @@
         <v>349.9999416666764</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="29">
@@ -2967,7 +2967,7 @@
         <v>1499.999250000375</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="30">
@@ -3025,7 +3025,7 @@
         <v>394.7367382271742</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="31">
@@ -3083,7 +3083,7 @@
         <v>1199.999760000048</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="32">
@@ -3141,7 +3141,7 @@
         <v>288.3434698332915</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="33">
@@ -3199,7 +3199,7 @@
         <v>489.9997550001225</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
     <row r="34">
@@ -3257,7 +3257,7 @@
         <v>2249.999718750035</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>45922.72111330232</v>
+        <v>45922.72836881405</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cargo_classification_results.xlsx
+++ b/output/reports/cargo_classification_results.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="大货物订单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="中货物订单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="小货物订单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="大货物订单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中货物订单" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="小货物订单" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -571,7 +571,7 @@
         <v>301.9348230405445</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         <v>255.8235097859207</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         <v>274.1853290686016</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         <v>2090.797481877377</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +899,7 @@
         <v>151.4285683381925</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="3">
@@ -957,7 +957,7 @@
         <v>230.1464830321325</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="4">
@@ -1015,7 +1015,7 @@
         <v>246.4285655612246</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="5">
@@ -1073,7 +1073,7 @@
         <v>147.6190441043085</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="6">
@@ -1131,7 +1131,7 @@
         <v>146.3888848225309</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1189,7 @@
         <v>799.9999466666703</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="8">
@@ -1247,7 +1247,7 @@
         <v>257.0260471626956</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
   </sheetData>
@@ -1401,7 +1401,7 @@
         <v>1549.666580574079</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="3">
@@ -1459,7 +1459,7 @@
         <v>558.1395132504065</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="4">
@@ -1517,7 +1517,7 @@
         <v>323.4210356094192</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="5">
@@ -1575,7 +1575,7 @@
         <v>338.6110922993837</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="6">
@@ -1633,7 +1633,7 @@
         <v>186.519454589224</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="7">
@@ -1691,7 +1691,7 @@
         <v>658.3079370971024</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="8">
@@ -1749,7 +1749,7 @@
         <v>364.166636319447</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="9">
@@ -1807,7 +1807,7 @@
         <v>337.9999774666682</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1865,7 @@
         <v>359.090876446284</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="11">
@@ -1923,7 +1923,7 @@
         <v>286.1110952160503</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="12">
@@ -1981,7 +1981,7 @@
         <v>372.4999689583359</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="13">
@@ -2039,7 +2039,7 @@
         <v>999.9998039216071</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="14">
@@ -2097,7 +2097,7 @@
         <v>339.1666384027802</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="15">
@@ -2155,7 +2155,7 @@
         <v>260.5768980214521</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="16">
@@ -2213,7 +2213,7 @@
         <v>199.3516856279023</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="17">
@@ -2271,7 +2271,7 @@
         <v>1115.999898545464</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="18">
@@ -2329,7 +2329,7 @@
         <v>280.8333099305575</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="19">
@@ -2387,7 +2387,7 @@
         <v>217.241371819263</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="20">
@@ -2445,7 +2445,7 @@
         <v>1190.475907029546</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="21">
@@ -2503,7 +2503,7 @@
         <v>363.3332929629674</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="22">
@@ -2561,7 +2561,7 @@
         <v>1124.99971875007</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="23">
@@ -2619,7 +2619,7 @@
         <v>256.2091168354095</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="24">
@@ -2677,7 +2677,7 @@
         <v>1333.332929293052</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="25">
@@ -2735,7 +2735,7 @@
         <v>1099.999633333455</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="26">
@@ -2793,7 +2793,7 @@
         <v>381.249952343756</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="27">
@@ -2851,7 +2851,7 @@
         <v>1133.332955555682</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="28">
@@ -2909,7 +2909,7 @@
         <v>349.9999416666764</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="29">
@@ -2967,7 +2967,7 @@
         <v>1499.999250000375</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="30">
@@ -3025,7 +3025,7 @@
         <v>394.7367382271742</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="31">
@@ -3083,7 +3083,7 @@
         <v>1199.999760000048</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="32">
@@ -3141,7 +3141,7 @@
         <v>288.3434698332915</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="33">
@@ -3199,7 +3199,7 @@
         <v>489.9997550001225</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
     <row r="34">
@@ -3257,7 +3257,7 @@
         <v>2249.999718750035</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>45922.72836881405</v>
+        <v>45922.73572173498</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cargo_classification_results.xlsx
+++ b/output/reports/cargo_classification_results.xlsx
@@ -571,7 +571,7 @@
         <v>301.9348230405445</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         <v>255.8235097859207</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         <v>274.1853290686016</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         <v>2090.797481877377</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +899,7 @@
         <v>151.4285683381925</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="3">
@@ -957,7 +957,7 @@
         <v>230.1464830321325</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="4">
@@ -1015,7 +1015,7 @@
         <v>246.4285655612246</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="5">
@@ -1073,7 +1073,7 @@
         <v>147.6190441043085</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="6">
@@ -1131,7 +1131,7 @@
         <v>146.3888848225309</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1189,7 @@
         <v>799.9999466666703</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="8">
@@ -1247,7 +1247,7 @@
         <v>257.0260471626956</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
   </sheetData>
@@ -1401,7 +1401,7 @@
         <v>1549.666580574079</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="3">
@@ -1459,7 +1459,7 @@
         <v>558.1395132504065</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="4">
@@ -1517,7 +1517,7 @@
         <v>323.4210356094192</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="5">
@@ -1575,7 +1575,7 @@
         <v>338.6110922993837</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="6">
@@ -1633,7 +1633,7 @@
         <v>186.519454589224</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="7">
@@ -1691,7 +1691,7 @@
         <v>658.3079370971024</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="8">
@@ -1749,7 +1749,7 @@
         <v>364.166636319447</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="9">
@@ -1807,7 +1807,7 @@
         <v>337.9999774666682</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1865,7 @@
         <v>359.090876446284</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="11">
@@ -1923,7 +1923,7 @@
         <v>286.1110952160503</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="12">
@@ -1981,7 +1981,7 @@
         <v>372.4999689583359</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="13">
@@ -2039,7 +2039,7 @@
         <v>999.9998039216071</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="14">
@@ -2097,7 +2097,7 @@
         <v>339.1666384027802</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="15">
@@ -2155,7 +2155,7 @@
         <v>260.5768980214521</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="16">
@@ -2213,7 +2213,7 @@
         <v>199.3516856279023</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="17">
@@ -2271,7 +2271,7 @@
         <v>1115.999898545464</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="18">
@@ -2329,7 +2329,7 @@
         <v>280.8333099305575</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="19">
@@ -2387,7 +2387,7 @@
         <v>217.241371819263</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="20">
@@ -2445,7 +2445,7 @@
         <v>1190.475907029546</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="21">
@@ -2503,7 +2503,7 @@
         <v>363.3332929629674</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="22">
@@ -2561,7 +2561,7 @@
         <v>1124.99971875007</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="23">
@@ -2619,7 +2619,7 @@
         <v>256.2091168354095</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="24">
@@ -2677,7 +2677,7 @@
         <v>1333.332929293052</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="25">
@@ -2735,7 +2735,7 @@
         <v>1099.999633333455</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="26">
@@ -2793,7 +2793,7 @@
         <v>381.249952343756</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="27">
@@ -2851,7 +2851,7 @@
         <v>1133.332955555682</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="28">
@@ -2909,7 +2909,7 @@
         <v>349.9999416666764</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="29">
@@ -2967,7 +2967,7 @@
         <v>1499.999250000375</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="30">
@@ -3025,7 +3025,7 @@
         <v>394.7367382271742</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="31">
@@ -3083,7 +3083,7 @@
         <v>1199.999760000048</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="32">
@@ -3141,7 +3141,7 @@
         <v>288.3434698332915</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="33">
@@ -3199,7 +3199,7 @@
         <v>489.9997550001225</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
     <row r="34">
@@ -3257,7 +3257,7 @@
         <v>2249.999718750035</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>45922.73572173498</v>
+        <v>45926.59161548105</v>
       </c>
     </row>
   </sheetData>

--- a/output/reports/cargo_classification_results.xlsx
+++ b/output/reports/cargo_classification_results.xlsx
@@ -571,7 +571,7 @@
         <v>301.9348230405445</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="3">
@@ -629,7 +629,7 @@
         <v>255.8235097859207</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         <v>274.1853290686016</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         <v>2090.797481877377</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +899,7 @@
         <v>151.4285683381925</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="3">
@@ -957,7 +957,7 @@
         <v>230.1464830321325</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="4">
@@ -1015,7 +1015,7 @@
         <v>246.4285655612246</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="5">
@@ -1073,7 +1073,7 @@
         <v>147.6190441043085</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="6">
@@ -1131,7 +1131,7 @@
         <v>146.3888848225309</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="7">
@@ -1189,7 +1189,7 @@
         <v>799.9999466666703</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="8">
@@ -1247,7 +1247,7 @@
         <v>257.0260471626956</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
   </sheetData>
@@ -1401,7 +1401,7 @@
         <v>1549.666580574079</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="3">
@@ -1459,7 +1459,7 @@
         <v>558.1395132504065</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="4">
@@ -1517,7 +1517,7 @@
         <v>323.4210356094192</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="5">
@@ -1575,7 +1575,7 @@
         <v>338.6110922993837</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="6">
@@ -1633,7 +1633,7 @@
         <v>186.519454589224</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="7">
@@ -1691,7 +1691,7 @@
         <v>658.3079370971024</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="8">
@@ -1749,7 +1749,7 @@
         <v>364.166636319447</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="9">
@@ -1807,7 +1807,7 @@
         <v>337.9999774666682</v>
       </c>
       <c r="P9" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="10">
@@ -1865,7 +1865,7 @@
         <v>359.090876446284</v>
       </c>
       <c r="P10" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="11">
@@ -1923,7 +1923,7 @@
         <v>286.1110952160503</v>
       </c>
       <c r="P11" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="12">
@@ -1981,7 +1981,7 @@
         <v>372.4999689583359</v>
       </c>
       <c r="P12" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="13">
@@ -2039,7 +2039,7 @@
         <v>999.9998039216071</v>
       </c>
       <c r="P13" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="14">
@@ -2097,7 +2097,7 @@
         <v>339.1666384027802</v>
       </c>
       <c r="P14" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="15">
@@ -2155,7 +2155,7 @@
         <v>260.5768980214521</v>
       </c>
       <c r="P15" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="16">
@@ -2213,7 +2213,7 @@
         <v>199.3516856279023</v>
       </c>
       <c r="P16" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="17">
@@ -2271,7 +2271,7 @@
         <v>1115.999898545464</v>
       </c>
       <c r="P17" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="18">
@@ -2329,7 +2329,7 @@
         <v>280.8333099305575</v>
       </c>
       <c r="P18" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="19">
@@ -2387,7 +2387,7 @@
         <v>217.241371819263</v>
       </c>
       <c r="P19" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="20">
@@ -2445,7 +2445,7 @@
         <v>1190.475907029546</v>
       </c>
       <c r="P20" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="21">
@@ -2503,7 +2503,7 @@
         <v>363.3332929629674</v>
       </c>
       <c r="P21" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="22">
@@ -2561,7 +2561,7 @@
         <v>1124.99971875007</v>
       </c>
       <c r="P22" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="23">
@@ -2619,7 +2619,7 @@
         <v>256.2091168354095</v>
       </c>
       <c r="P23" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="24">
@@ -2677,7 +2677,7 @@
         <v>1333.332929293052</v>
       </c>
       <c r="P24" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="25">
@@ -2735,7 +2735,7 @@
         <v>1099.999633333455</v>
       </c>
       <c r="P25" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="26">
@@ -2793,7 +2793,7 @@
         <v>381.249952343756</v>
       </c>
       <c r="P26" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="27">
@@ -2851,7 +2851,7 @@
         <v>1133.332955555682</v>
       </c>
       <c r="P27" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="28">
@@ -2909,7 +2909,7 @@
         <v>349.9999416666764</v>
       </c>
       <c r="P28" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="29">
@@ -2967,7 +2967,7 @@
         <v>1499.999250000375</v>
       </c>
       <c r="P29" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="30">
@@ -3025,7 +3025,7 @@
         <v>394.7367382271742</v>
       </c>
       <c r="P30" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="31">
@@ -3083,7 +3083,7 @@
         <v>1199.999760000048</v>
       </c>
       <c r="P31" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="32">
@@ -3141,7 +3141,7 @@
         <v>288.3434698332915</v>
       </c>
       <c r="P32" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="33">
@@ -3199,7 +3199,7 @@
         <v>489.9997550001225</v>
       </c>
       <c r="P33" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
     <row r="34">
@@ -3257,7 +3257,7 @@
         <v>2249.999718750035</v>
       </c>
       <c r="P34" s="2" t="n">
-        <v>45926.59161548105</v>
+        <v>45947.74746114826</v>
       </c>
     </row>
   </sheetData>
